--- a/test_data/business_scenarios.xlsx
+++ b/test_data/business_scenarios.xlsx
@@ -666,14 +666,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sales Trend</t>
+          <t>Total Sales</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Same Day</t>
+          <t>Second Class</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Seattle</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">

--- a/test_data/business_scenarios.xlsx
+++ b/test_data/business_scenarios.xlsx
@@ -1,90 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rishabhbhangale/Downloads/semantics/FieldTrace/test_playwright combined/test_data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AFCFABF-5D5F-2B4C-A2A8-A5006BA5E53E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>Test ID</t>
-  </si>
-  <si>
-    <t>Scenario Name</t>
-  </si>
-  <si>
-    <t>Slicer 1 Name</t>
-  </si>
-  <si>
-    <t>Slicer 1 Value</t>
-  </si>
-  <si>
-    <t>Slicer 2 Name</t>
-  </si>
-  <si>
-    <t>Slicer 2 Value</t>
-  </si>
-  <si>
-    <t>KPI to Read</t>
-  </si>
-  <si>
-    <t>SQL File Name</t>
-  </si>
-  <si>
-    <t>TC-BIZ-001</t>
-  </si>
-  <si>
-    <t>State-Level Sales Validation</t>
-  </si>
-  <si>
-    <t>State</t>
-  </si>
-  <si>
-    <t>California</t>
-  </si>
-  <si>
-    <t>Total Sales</t>
-  </si>
-  <si>
-    <t>tc001.sql</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -99,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -423,54 +420,152 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Scenario Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Slicer 1 Name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Slicer 1 Value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Slicer 2 Name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Slicer 2 Value</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Slicer 3 Name</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Slicer 3 Value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Slicer 4 Name</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Slicer 4 Value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Slicer 5 Name</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Slicer 5 Value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Slicer 6 Name</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Slicer 6 Value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>KPI to Read</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>SQL File Name</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TC-BIZ-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>State-Level Sales Validation</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Ship Mode</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Standard Class</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Sub-Category</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Phones</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Total Sales</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>tc001.sql</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/test_data/business_scenarios.xlsx
+++ b/test_data/business_scenarios.xlsx
@@ -1,13 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,7 +25,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,10 +50,19 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -62,7 +75,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -425,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,12 +564,6 @@
           <t>Phones</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>Total Sales</t>
@@ -565,10 +572,426 @@
       <c r="P2" t="inlineStr">
         <is>
           <t>tc001.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TC-BIZ-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Customer Segment Analysis</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Customer Segment</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ship Mode</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Standard Class</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Sub-Category</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Phones</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Total Sales</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>tc002.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TC-BIZ-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Category Level Profit</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ship Mode</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Standard Class</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sub-Category</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Phones</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Total Profit</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>tc003.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TC-BIZ-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Standard Class Order Count</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ship Mode</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Standard Class</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t># of Orders</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>tc004.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TC-BIZ-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sub-Category Discount Impact</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Sub-Category</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Chairs</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Customer Segment</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ship Mode</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Standard Class</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Total Profit</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>tc005.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TC-BIZ-006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>State-Level Phones Sales (Texas)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Texas</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Ship Mode</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Standard Class</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sub-Category</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Phones</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Total Sales</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>tc006.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TC-BIZ-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>High Profit Customers</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Customer Segment</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Home Office</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Texas</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ship Mode</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Standard Class</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sub-Category</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Phones</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Total Profit</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>tc007.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TC-BIZ-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Second Class Shipping Analysis</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sub-Category</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Chairs</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Ship Mode</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Second Class</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t># of Orders</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>tc008.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TC-BIZ-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Low Discount Cities (was Regions)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ship Mode</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Standard Class</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sub-Category</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Phones</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Total Profit</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>tc009.sql</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/test_data/business_scenarios.xlsx
+++ b/test_data/business_scenarios.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rishabhbhangale/Downloads/semantics/FieldTrace/test_playwright combined/test_data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82F031A-CD47-7C42-B8DA-1946DBD8E749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="660" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="60">
   <si>
     <t>Test ID</t>
   </si>
@@ -73,56 +67,140 @@
     <t>TC-BIZ-001</t>
   </si>
   <si>
+    <t>TC-BIZ-002</t>
+  </si>
+  <si>
+    <t>TC-BIZ-003</t>
+  </si>
+  <si>
+    <t>TC-BIZ-004</t>
+  </si>
+  <si>
+    <t>TC-BIZ-005</t>
+  </si>
+  <si>
+    <t>TC-BIZ-006</t>
+  </si>
+  <si>
+    <t>TC-BIZ-007</t>
+  </si>
+  <si>
+    <t>TC-BIZ-008</t>
+  </si>
+  <si>
     <t>State-Level Sales Validation</t>
   </si>
   <si>
+    <t>Customer Segment Analysis</t>
+  </si>
+  <si>
+    <t>City-Level Profit Validation</t>
+  </si>
+  <si>
+    <t>Sales by Ship Mode Validation</t>
+  </si>
+  <si>
+    <t>Texas Phones Sales Validation</t>
+  </si>
+  <si>
+    <t>Home Office Phones Profit - Texas</t>
+  </si>
+  <si>
+    <t>Chairs Orders - Second Class Shipping</t>
+  </si>
+  <si>
+    <t>LA Phones Profit Validation</t>
+  </si>
+  <si>
     <t>State</t>
   </si>
   <si>
+    <t>Customer Segment</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Ship Mode</t>
+  </si>
+  <si>
     <t>California</t>
   </si>
   <si>
-    <t>Ship Mode</t>
+    <t>Corporate</t>
+  </si>
+  <si>
+    <t>Los Angeles</t>
   </si>
   <si>
     <t>Standard Class</t>
   </si>
   <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>Home Office</t>
+  </si>
+  <si>
+    <t>Second Class</t>
+  </si>
+  <si>
     <t>Sub-Category</t>
   </si>
   <si>
+    <t>Illinois</t>
+  </si>
+  <si>
     <t>Phones</t>
   </si>
   <si>
+    <t>Chairs</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
     <t>Total Sales</t>
   </si>
   <si>
+    <t>Total Profit</t>
+  </si>
+  <si>
+    <t># of Orders</t>
+  </si>
+  <si>
     <t>tc001.sql</t>
   </si>
   <si>
-    <t>TC-BIZ-002</t>
-  </si>
-  <si>
-    <t>Customer Segment Analysis</t>
-  </si>
-  <si>
-    <t>Customer Segment</t>
-  </si>
-  <si>
-    <t>Corporate</t>
-  </si>
-  <si>
-    <t>Illinois</t>
-  </si>
-  <si>
     <t>tc002.sql</t>
+  </si>
+  <si>
+    <t>tc003.sql</t>
+  </si>
+  <si>
+    <t>tc004.sql</t>
+  </si>
+  <si>
+    <t>tc006.sql</t>
+  </si>
+  <si>
+    <t>tc007.sql</t>
+  </si>
+  <si>
+    <t>tc008.sql</t>
+  </si>
+  <si>
+    <t>tc009.sql</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -185,14 +263,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -480,11 +550,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -534,74 +604,254 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
         <v>16</v>
       </c>
       <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" t="s">
+        <v>49</v>
+      </c>
+      <c r="P2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O3" t="s">
+        <v>49</v>
+      </c>
+      <c r="P3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" t="s">
+        <v>45</v>
+      </c>
+      <c r="O4" t="s">
+        <v>50</v>
+      </c>
+      <c r="P4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s">
+        <v>39</v>
+      </c>
+      <c r="O5" t="s">
+        <v>49</v>
+      </c>
+      <c r="P5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" t="s">
         <v>20</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" t="s">
+        <v>45</v>
+      </c>
+      <c r="O6" t="s">
+        <v>49</v>
+      </c>
+      <c r="P6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" t="s">
         <v>21</v>
       </c>
-      <c r="G2" t="s">
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" t="s">
+        <v>45</v>
+      </c>
+      <c r="O7" t="s">
+        <v>50</v>
+      </c>
+      <c r="P7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" t="s">
         <v>22</v>
       </c>
-      <c r="H2" t="s">
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" t="s">
+        <v>46</v>
+      </c>
+      <c r="O8" t="s">
+        <v>51</v>
+      </c>
+      <c r="P8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" t="s">
         <v>23</v>
       </c>
-      <c r="O2" t="s">
-        <v>24</v>
-      </c>
-      <c r="P2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O3" t="s">
-        <v>24</v>
-      </c>
-      <c r="P3" t="s">
+      <c r="B9" t="s">
         <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" t="s">
+        <v>45</v>
+      </c>
+      <c r="O9" t="s">
+        <v>50</v>
+      </c>
+      <c r="P9" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/test_data/business_scenarios.xlsx
+++ b/test_data/business_scenarios.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rishabhbhangale/Downloads/semantics/FieldTrace/test_playwright combined/test_data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A8EE34-F107-7346-9B14-B0643C19F486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="660" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
   <si>
     <t>Test ID</t>
   </si>
@@ -67,140 +73,95 @@
     <t>TC-BIZ-001</t>
   </si>
   <si>
-    <t>TC-BIZ-002</t>
-  </si>
-  <si>
-    <t>TC-BIZ-003</t>
-  </si>
-  <si>
     <t>TC-BIZ-004</t>
   </si>
   <si>
+    <t>State-Level Sales Validation</t>
+  </si>
+  <si>
+    <t>Sales by Ship Mode Validation</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Ship Mode</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>Standard Class</t>
+  </si>
+  <si>
+    <t>Sub-Category</t>
+  </si>
+  <si>
+    <t>Phones</t>
+  </si>
+  <si>
+    <t>Total Sales</t>
+  </si>
+  <si>
+    <t>tc001.sql</t>
+  </si>
+  <si>
+    <t>tc004.sql</t>
+  </si>
+  <si>
     <t>TC-BIZ-005</t>
   </si>
   <si>
+    <t>Texas Phones Sales Validation</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>tc006.sql</t>
+  </si>
+  <si>
     <t>TC-BIZ-006</t>
   </si>
   <si>
+    <t>Home Office Phones Profit - Texas</t>
+  </si>
+  <si>
+    <t>Customer Segment</t>
+  </si>
+  <si>
+    <t>Home Office</t>
+  </si>
+  <si>
+    <t>Total Profit</t>
+  </si>
+  <si>
+    <t>tc007.sql</t>
+  </si>
+  <si>
     <t>TC-BIZ-007</t>
   </si>
   <si>
-    <t>TC-BIZ-008</t>
-  </si>
-  <si>
-    <t>State-Level Sales Validation</t>
-  </si>
-  <si>
-    <t>Customer Segment Analysis</t>
-  </si>
-  <si>
-    <t>City-Level Profit Validation</t>
-  </si>
-  <si>
-    <t>Sales by Ship Mode Validation</t>
-  </si>
-  <si>
-    <t>Texas Phones Sales Validation</t>
-  </si>
-  <si>
-    <t>Home Office Phones Profit - Texas</t>
-  </si>
-  <si>
     <t>Chairs Orders - Second Class Shipping</t>
   </si>
   <si>
-    <t>LA Phones Profit Validation</t>
-  </si>
-  <si>
-    <t>State</t>
-  </si>
-  <si>
-    <t>Customer Segment</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>Ship Mode</t>
-  </si>
-  <si>
-    <t>California</t>
-  </si>
-  <si>
-    <t>Corporate</t>
-  </si>
-  <si>
-    <t>Los Angeles</t>
-  </si>
-  <si>
-    <t>Standard Class</t>
-  </si>
-  <si>
-    <t>Texas</t>
-  </si>
-  <si>
-    <t>Home Office</t>
-  </si>
-  <si>
     <t>Second Class</t>
   </si>
   <si>
-    <t>Sub-Category</t>
-  </si>
-  <si>
-    <t>Illinois</t>
-  </si>
-  <si>
-    <t>Phones</t>
-  </si>
-  <si>
     <t>Chairs</t>
   </si>
   <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t>Total Sales</t>
-  </si>
-  <si>
-    <t>Total Profit</t>
-  </si>
-  <si>
     <t># of Orders</t>
   </si>
   <si>
-    <t>tc001.sql</t>
-  </si>
-  <si>
-    <t>tc002.sql</t>
-  </si>
-  <si>
-    <t>tc003.sql</t>
-  </si>
-  <si>
-    <t>tc004.sql</t>
-  </si>
-  <si>
-    <t>tc006.sql</t>
-  </si>
-  <si>
-    <t>tc007.sql</t>
-  </si>
-  <si>
-    <t>tc008.sql</t>
-  </si>
-  <si>
-    <t>tc009.sql</t>
+    <t>tc005.sql</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -263,13 +224,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -307,7 +276,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -341,6 +310,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -375,9 +345,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -550,11 +521,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:P6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -604,254 +575,146 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
       <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" t="s">
         <v>24</v>
       </c>
-      <c r="C2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G2" t="s">
-        <v>43</v>
-      </c>
       <c r="H2" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="O2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="P2" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
       <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O3" t="s">
+        <v>26</v>
+      </c>
+      <c r="P3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
         <v>25</v>
       </c>
-      <c r="C3" t="s">
+      <c r="O4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>33</v>
       </c>
-      <c r="D3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I3" t="s">
-        <v>43</v>
-      </c>
-      <c r="J3" t="s">
-        <v>45</v>
-      </c>
-      <c r="O3" t="s">
-        <v>49</v>
-      </c>
-      <c r="P3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B5" t="s">
         <v>34</v>
-      </c>
-      <c r="D4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I4" t="s">
-        <v>43</v>
-      </c>
-      <c r="J4" t="s">
-        <v>45</v>
-      </c>
-      <c r="O4" t="s">
-        <v>50</v>
-      </c>
-      <c r="P4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
       </c>
       <c r="C5" t="s">
         <v>35</v>
       </c>
       <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O5" t="s">
+        <v>37</v>
+      </c>
+      <c r="P5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>39</v>
       </c>
-      <c r="O5" t="s">
-        <v>49</v>
-      </c>
-      <c r="P5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" t="s">
+        <v>42</v>
+      </c>
+      <c r="O6" t="s">
         <v>43</v>
       </c>
-      <c r="F6" t="s">
-        <v>45</v>
-      </c>
-      <c r="O6" t="s">
-        <v>49</v>
-      </c>
       <c r="P6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" t="s">
-        <v>43</v>
-      </c>
-      <c r="J7" t="s">
-        <v>45</v>
-      </c>
-      <c r="O7" t="s">
-        <v>50</v>
-      </c>
-      <c r="P7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" t="s">
-        <v>46</v>
-      </c>
-      <c r="O8" t="s">
-        <v>51</v>
-      </c>
-      <c r="P8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="A9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s">
         <v>38</v>
-      </c>
-      <c r="E9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O9" t="s">
-        <v>50</v>
-      </c>
-      <c r="P9" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/test_data/business_scenarios.xlsx
+++ b/test_data/business_scenarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rishabhbhangale/Downloads/semantics/FieldTrace/test_playwright combined/test_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A8EE34-F107-7346-9B14-B0643C19F486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_B9865CC697D9AECF8A160BCA133F10484292E67C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="660" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="43">
   <si>
     <t>Test ID</t>
   </si>
@@ -76,85 +76,79 @@
     <t>TC-BIZ-004</t>
   </si>
   <si>
+    <t>TC-BIZ-005</t>
+  </si>
+  <si>
+    <t>TC-BIZ-006</t>
+  </si>
+  <si>
+    <t>TC-BIZ-007</t>
+  </si>
+  <si>
     <t>State-Level Sales Validation</t>
   </si>
   <si>
     <t>Sales by Ship Mode Validation</t>
   </si>
   <si>
+    <t>Texas Phones Sales Validation</t>
+  </si>
+  <si>
+    <t>Home Office Phones Profit - Texas</t>
+  </si>
+  <si>
+    <t>Chairs Orders - Second Class Shipping</t>
+  </si>
+  <si>
     <t>State</t>
   </si>
   <si>
     <t>Ship Mode</t>
   </si>
   <si>
+    <t>Customer Segment</t>
+  </si>
+  <si>
     <t>California</t>
   </si>
   <si>
     <t>Standard Class</t>
   </si>
   <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>Home Office</t>
+  </si>
+  <si>
+    <t>Second Class</t>
+  </si>
+  <si>
     <t>Sub-Category</t>
   </si>
   <si>
     <t>Phones</t>
   </si>
   <si>
+    <t>Chairs</t>
+  </si>
+  <si>
     <t>Total Sales</t>
   </si>
   <si>
-    <t>tc001.sql</t>
-  </si>
-  <si>
-    <t>tc004.sql</t>
-  </si>
-  <si>
-    <t>TC-BIZ-005</t>
-  </si>
-  <si>
-    <t>Texas Phones Sales Validation</t>
-  </si>
-  <si>
-    <t>Texas</t>
+    <t>Total Profit</t>
+  </si>
+  <si>
+    <t># of Orders</t>
   </si>
   <si>
     <t>tc006.sql</t>
   </si>
   <si>
-    <t>TC-BIZ-006</t>
-  </si>
-  <si>
-    <t>Home Office Phones Profit - Texas</t>
-  </si>
-  <si>
-    <t>Customer Segment</t>
-  </si>
-  <si>
-    <t>Home Office</t>
-  </si>
-  <si>
-    <t>Total Profit</t>
-  </si>
-  <si>
     <t>tc007.sql</t>
   </si>
   <si>
-    <t>TC-BIZ-007</t>
-  </si>
-  <si>
-    <t>Chairs Orders - Second Class Shipping</t>
-  </si>
-  <si>
-    <t>Second Class</t>
-  </si>
-  <si>
-    <t>Chairs</t>
-  </si>
-  <si>
-    <t># of Orders</t>
-  </si>
-  <si>
-    <t>tc005.sql</t>
+    <t>tc008.sql</t>
   </si>
 </sst>
 </file>
@@ -580,31 +574,28 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="O2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
@@ -612,109 +603,106 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="O3" t="s">
-        <v>26</v>
-      </c>
-      <c r="P3" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
         <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="O4" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="P4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F5" t="s">
         <v>31</v>
       </c>
       <c r="G5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I5" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J5" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="O5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P5" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="O6" t="s">
         <v>39</v>
       </c>
-      <c r="B6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="P6" t="s">
         <v>42</v>
-      </c>
-      <c r="O6" t="s">
-        <v>43</v>
-      </c>
-      <c r="P6" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/test_data/business_scenarios.xlsx
+++ b/test_data/business_scenarios.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rishabhbhangale/Downloads/semantics/FieldTrace/test_playwright combined/test_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rishabhbhangale/Downloads/semantics/test_playwright combined/test_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_B9865CC697D9AECF8A160BCA133F10484292E67C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5AB1076-15FD-2F46-95B6-5EC916445061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="660" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="40">
   <si>
     <t>Test ID</t>
   </si>
@@ -28,6 +28,54 @@
     <t>Scenario Name</t>
   </si>
   <si>
+    <t>KPI to Read</t>
+  </si>
+  <si>
+    <t>SQL File Name</t>
+  </si>
+  <si>
+    <t>TC-BIZ-001</t>
+  </si>
+  <si>
+    <t>TC-BIZ-004</t>
+  </si>
+  <si>
+    <t>TC-BIZ-005</t>
+  </si>
+  <si>
+    <t>TC-BIZ-006</t>
+  </si>
+  <si>
+    <t>TC-BIZ-007</t>
+  </si>
+  <si>
+    <t>State-Level Sales Validation</t>
+  </si>
+  <si>
+    <t>Sales by Ship Mode Validation</t>
+  </si>
+  <si>
+    <t>Texas Phones Sales Validation</t>
+  </si>
+  <si>
+    <t>Home Office Phones Profit - Texas</t>
+  </si>
+  <si>
+    <t>Chairs Orders - Second Class Shipping</t>
+  </si>
+  <si>
+    <t>Total Sales</t>
+  </si>
+  <si>
+    <t>Total Profit</t>
+  </si>
+  <si>
+    <t># of Orders</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
     <t>Slicer 1 Name</t>
   </si>
   <si>
@@ -64,91 +112,34 @@
     <t>Slicer 6 Value</t>
   </si>
   <si>
-    <t>KPI to Read</t>
-  </si>
-  <si>
-    <t>SQL File Name</t>
-  </si>
-  <si>
-    <t>TC-BIZ-001</t>
-  </si>
-  <si>
-    <t>TC-BIZ-004</t>
-  </si>
-  <si>
-    <t>TC-BIZ-005</t>
-  </si>
-  <si>
-    <t>TC-BIZ-006</t>
-  </si>
-  <si>
-    <t>TC-BIZ-007</t>
-  </si>
-  <si>
-    <t>State-Level Sales Validation</t>
-  </si>
-  <si>
-    <t>Sales by Ship Mode Validation</t>
-  </si>
-  <si>
-    <t>Texas Phones Sales Validation</t>
-  </si>
-  <si>
-    <t>Home Office Phones Profit - Texas</t>
-  </si>
-  <si>
-    <t>Chairs Orders - Second Class Shipping</t>
-  </si>
-  <si>
-    <t>State</t>
+    <t>California</t>
   </si>
   <si>
     <t>Ship Mode</t>
   </si>
   <si>
+    <t>Standard Class</t>
+  </si>
+  <si>
+    <t>Sub-Category</t>
+  </si>
+  <si>
+    <t>Phones</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
     <t>Customer Segment</t>
   </si>
   <si>
-    <t>California</t>
-  </si>
-  <si>
-    <t>Standard Class</t>
-  </si>
-  <si>
-    <t>Texas</t>
-  </si>
-  <si>
     <t>Home Office</t>
   </si>
   <si>
     <t>Second Class</t>
   </si>
   <si>
-    <t>Sub-Category</t>
-  </si>
-  <si>
-    <t>Phones</t>
-  </si>
-  <si>
     <t>Chairs</t>
-  </si>
-  <si>
-    <t>Total Sales</t>
-  </si>
-  <si>
-    <t>Total Profit</t>
-  </si>
-  <si>
-    <t># of Orders</t>
-  </si>
-  <si>
-    <t>tc006.sql</t>
-  </si>
-  <si>
-    <t>tc007.sql</t>
-  </si>
-  <si>
-    <t>tc008.sql</t>
   </si>
 </sst>
 </file>
@@ -527,182 +518,173 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" t="s">
         <v>34</v>
       </c>
-      <c r="H2" t="s">
-        <v>35</v>
-      </c>
       <c r="O2" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O3" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
         <v>34</v>
       </c>
-      <c r="F4" t="s">
-        <v>35</v>
-      </c>
       <c r="O4" t="s">
-        <v>37</v>
-      </c>
-      <c r="P4" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" t="s">
         <v>32</v>
       </c>
-      <c r="E5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" t="s">
-        <v>30</v>
-      </c>
       <c r="I5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" t="s">
         <v>34</v>
       </c>
-      <c r="J5" t="s">
-        <v>35</v>
-      </c>
       <c r="O5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P5" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" t="s">
         <v>33</v>
       </c>
-      <c r="E6" t="s">
-        <v>34</v>
-      </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="O6" t="s">
-        <v>39</v>
-      </c>
-      <c r="P6" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/test_data/business_scenarios.xlsx
+++ b/test_data/business_scenarios.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10810"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rishabhbhangale/Downloads/semantics/test_playwright combined/test_data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5AB1076-15FD-2F46-95B6-5EC916445061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -28,6 +22,42 @@
     <t>Scenario Name</t>
   </si>
   <si>
+    <t>Slicer 1 Name</t>
+  </si>
+  <si>
+    <t>Slicer 1 Value</t>
+  </si>
+  <si>
+    <t>Slicer 2 Name</t>
+  </si>
+  <si>
+    <t>Slicer 2 Value</t>
+  </si>
+  <si>
+    <t>Slicer 3 Name</t>
+  </si>
+  <si>
+    <t>Slicer 3 Value</t>
+  </si>
+  <si>
+    <t>Slicer 4 Name</t>
+  </si>
+  <si>
+    <t>Slicer 4 Value</t>
+  </si>
+  <si>
+    <t>Slicer 5 Name</t>
+  </si>
+  <si>
+    <t>Slicer 5 Value</t>
+  </si>
+  <si>
+    <t>Slicer 6 Name</t>
+  </si>
+  <si>
+    <t>Slicer 6 Value</t>
+  </si>
+  <si>
     <t>KPI to Read</t>
   </si>
   <si>
@@ -64,6 +94,39 @@
     <t>Chairs Orders - Second Class Shipping</t>
   </si>
   <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Ship Mode</t>
+  </si>
+  <si>
+    <t>Customer Segment</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>Standard Class</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>Home Office</t>
+  </si>
+  <si>
+    <t>Second Class</t>
+  </si>
+  <si>
+    <t>Sub-Category</t>
+  </si>
+  <si>
+    <t>Phones</t>
+  </si>
+  <si>
+    <t>Chairs</t>
+  </si>
+  <si>
     <t>Total Sales</t>
   </si>
   <si>
@@ -71,82 +134,13 @@
   </si>
   <si>
     <t># of Orders</t>
-  </si>
-  <si>
-    <t>State</t>
-  </si>
-  <si>
-    <t>Slicer 1 Name</t>
-  </si>
-  <si>
-    <t>Slicer 1 Value</t>
-  </si>
-  <si>
-    <t>Slicer 2 Name</t>
-  </si>
-  <si>
-    <t>Slicer 2 Value</t>
-  </si>
-  <si>
-    <t>Slicer 3 Name</t>
-  </si>
-  <si>
-    <t>Slicer 3 Value</t>
-  </si>
-  <si>
-    <t>Slicer 4 Name</t>
-  </si>
-  <si>
-    <t>Slicer 4 Value</t>
-  </si>
-  <si>
-    <t>Slicer 5 Name</t>
-  </si>
-  <si>
-    <t>Slicer 5 Value</t>
-  </si>
-  <si>
-    <t>Slicer 6 Name</t>
-  </si>
-  <si>
-    <t>Slicer 6 Value</t>
-  </si>
-  <si>
-    <t>California</t>
-  </si>
-  <si>
-    <t>Ship Mode</t>
-  </si>
-  <si>
-    <t>Standard Class</t>
-  </si>
-  <si>
-    <t>Sub-Category</t>
-  </si>
-  <si>
-    <t>Phones</t>
-  </si>
-  <si>
-    <t>Texas</t>
-  </si>
-  <si>
-    <t>Customer Segment</t>
-  </si>
-  <si>
-    <t>Home Office</t>
-  </si>
-  <si>
-    <t>Second Class</t>
-  </si>
-  <si>
-    <t>Chairs</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -209,21 +203,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -261,7 +247,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -295,7 +281,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -330,10 +315,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -506,11 +490,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -518,173 +502,173 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" t="s">
+        <v>35</v>
+      </c>
+      <c r="O2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s">
+        <v>35</v>
+      </c>
+      <c r="O4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" t="s">
+        <v>35</v>
+      </c>
+      <c r="O5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="B6" t="s">
         <v>25</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L1" s="1" t="s">
+      <c r="C6" t="s">
         <v>27</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="D6" t="s">
         <v>33</v>
       </c>
-      <c r="H2" t="s">
+      <c r="E6" t="s">
         <v>34</v>
       </c>
-      <c r="O2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-      <c r="O3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" t="s">
-        <v>34</v>
-      </c>
-      <c r="O4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="F6" t="s">
         <v>36</v>
       </c>
-      <c r="D5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" t="s">
-        <v>33</v>
-      </c>
-      <c r="J5" t="s">
-        <v>34</v>
-      </c>
-      <c r="O5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="O6" t="s">
         <v>39</v>
-      </c>
-      <c r="O6" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
